--- a/data/gravel/Parlee Taos 2025.xlsx
+++ b/data/gravel/Parlee Taos 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558BD39A-CF0E-304B-8891-E956AEE8CC91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF9F3CD-AD66-7A46-B263-D224437867B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="29500" yWindow="-17320" windowWidth="25960" windowHeight="16780" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -351,6 +351,9 @@
   </si>
   <si>
     <t>a8:h34</t>
+  </si>
+  <si>
+    <t>https://www.parleecycles.com/cdn/shop/files/IMG_6610.jpg?v=1757962057&amp;width=600</t>
   </si>
 </sst>
 </file>
@@ -773,6 +776,11 @@
         <v>89</v>
       </c>
     </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>106</v>
+      </c>
+    </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Parlee Taos 2025.xlsx
+++ b/data/gravel/Parlee Taos 2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF9F3CD-AD66-7A46-B263-D224437867B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A135D7-EAD1-D945-9C48-7313D28F51D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16300" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="109">
   <si>
     <t>brand</t>
   </si>
@@ -293,9 +293,6 @@
     <t>size</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>Parlee</t>
   </si>
   <si>
@@ -354,6 +351,15 @@
   </si>
   <si>
     <t>https://www.parleecycles.com/cdn/shop/files/IMG_6610.jpg?v=1757962057&amp;width=600</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Beverly, Massachusetts, USA</t>
   </si>
 </sst>
 </file>
@@ -729,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X74"/>
+  <dimension ref="A1:X75"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -741,7 +747,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
@@ -749,7 +755,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
@@ -773,12 +779,12 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
@@ -786,13 +792,13 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>85</v>
       </c>
       <c r="K7" s="5" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>8</v>
@@ -801,25 +807,25 @@
         <v>10</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O7" s="5" t="s">
         <v>77</v>
       </c>
       <c r="P7" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q7" s="5" t="s">
         <v>97</v>
-      </c>
-      <c r="Q7" s="5" t="s">
-        <v>98</v>
       </c>
       <c r="R7" s="5" t="s">
         <v>78</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T7" s="5" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="U7" s="5" t="s">
         <v>79</v>
@@ -831,7 +837,7 @@
         <v>80</v>
       </c>
       <c r="X7" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
@@ -842,25 +848,25 @@
         <v>85</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>76</v>
       </c>
       <c r="E8" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="F8" s="7" t="s">
         <v>91</v>
       </c>
-      <c r="F8" s="7" t="s">
+      <c r="G8" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="G8" s="7" t="s">
+      <c r="H8" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="H8" s="7" t="s">
-        <v>94</v>
-      </c>
       <c r="J8" s="5" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="K8" s="6">
         <v>508</v>
@@ -887,7 +893,7 @@
         <v>82</v>
       </c>
       <c r="S8" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T8" s="6">
         <v>700</v>
@@ -910,7 +916,7 @@
         <v>12</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C9" s="8">
         <v>508</v>
@@ -958,7 +964,7 @@
         <v>80</v>
       </c>
       <c r="S9" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T9" s="6">
         <v>735</v>
@@ -1002,7 +1008,7 @@
         <v>429</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="K10" s="6">
         <v>553</v>
@@ -1029,7 +1035,7 @@
         <v>80</v>
       </c>
       <c r="S10" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T10" s="6">
         <v>765</v>
@@ -1073,7 +1079,7 @@
         <v>640</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="K11" s="6">
         <v>577</v>
@@ -1100,7 +1106,7 @@
         <v>80</v>
       </c>
       <c r="S11" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T11" s="6">
         <v>791</v>
@@ -1123,7 +1129,7 @@
         <v>17</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="C12" s="8">
         <v>68.75</v>
@@ -1144,7 +1150,7 @@
         <v>69.75</v>
       </c>
       <c r="J12" s="5" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="K12" s="6">
         <v>602</v>
@@ -1171,7 +1177,7 @@
         <v>80</v>
       </c>
       <c r="S12" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T12" s="6">
         <v>810</v>
@@ -1215,7 +1221,7 @@
         <v>73.5</v>
       </c>
       <c r="J13" s="5" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="K13" s="6">
         <v>620</v>
@@ -1242,7 +1248,7 @@
         <v>80</v>
       </c>
       <c r="S13" s="6" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T13" s="6">
         <v>833</v>
@@ -1265,7 +1271,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="C14" s="8">
         <v>364</v>
@@ -1291,7 +1297,7 @@
         <v>15</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C15" s="8">
         <v>430</v>
@@ -1343,7 +1349,7 @@
         <v>20</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C17" s="8">
         <v>45</v>
@@ -1364,22 +1370,22 @@
         <v>45</v>
       </c>
       <c r="J17" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K17" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L17" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M17" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N17" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O17" s="8" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.3">
@@ -1387,7 +1393,7 @@
         <v>24</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C18" s="8">
         <v>700</v>
@@ -1491,7 +1497,7 @@
         <v>19</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C22" s="8">
         <v>425</v>
@@ -1763,7 +1769,7 @@
         <v>46</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
@@ -1823,7 +1829,7 @@
         <v>55</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
@@ -1831,7 +1837,7 @@
         <v>56</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
@@ -1923,7 +1929,15 @@
         <v>69</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>86</v>
+        <v>106</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="B75" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Parlee Taos 2025.xlsx
+++ b/data/gravel/Parlee Taos 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71A135D7-EAD1-D945-9C48-7313D28F51D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83429AE5-B98C-5842-92C9-1A482B567F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="16300" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -360,6 +360,24 @@
   </si>
   <si>
     <t>Beverly, Massachusetts, USA</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -735,7 +753,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X75"/>
+  <dimension ref="A1:X81"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1766,177 +1784,207 @@
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>46</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>47</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>48</v>
-      </c>
-      <c r="B53">
-        <v>31.6</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>49</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>84</v>
+        <v>112</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>50</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>51</v>
+        <v>114</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>52</v>
-      </c>
-      <c r="B57">
-        <v>180</v>
+        <v>46</v>
+      </c>
+      <c r="B57" s="1" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>53</v>
-      </c>
-      <c r="B58">
-        <v>160</v>
+        <v>47</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>54</v>
+        <v>48</v>
+      </c>
+      <c r="B59">
+        <v>31.6</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>102</v>
+        <v>84</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>56</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>102</v>
+        <v>50</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>57</v>
+        <v>51</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>58</v>
-      </c>
-      <c r="B63" s="1" t="s">
-        <v>84</v>
+        <v>52</v>
+      </c>
+      <c r="B63">
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="B64">
-        <v>2</v>
+        <v>160</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>60</v>
-      </c>
-      <c r="B65">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>62</v>
+        <v>56</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>63</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>84</v>
+        <v>57</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>65</v>
+        <v>59</v>
+      </c>
+      <c r="B70">
+        <v>2</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>66</v>
+        <v>60</v>
       </c>
       <c r="B71">
-        <v>4790</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>67</v>
-      </c>
-      <c r="B72">
-        <v>7190</v>
+        <v>61</v>
+      </c>
+      <c r="B72" s="1" t="s">
+        <v>84</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>68</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>84</v>
+        <v>62</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>63</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>66</v>
+      </c>
+      <c r="B77">
+        <v>4790</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>67</v>
+      </c>
+      <c r="B78">
+        <v>7190</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>68</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>69</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A75" s="1" t="s">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B81" t="s">
         <v>108</v>
       </c>
     </row>
